--- a/Другое/2026/Доходы.xlsx
+++ b/Другое/2026/Доходы.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="11">
   <si>
     <t>Дата</t>
   </si>
@@ -906,9 +906,15 @@
       <c r="C20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="14"/>
+      <c r="D20" s="12">
+        <v>46217</v>
+      </c>
+      <c r="E20" s="13">
+        <v>37634</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" thickBot="1">
       <c r="A21" s="3">
@@ -921,7 +927,9 @@
         <v>3</v>
       </c>
       <c r="D21" s="12"/>
-      <c r="E21" s="13"/>
+      <c r="E21" s="13">
+        <v>35000</v>
+      </c>
       <c r="F21" s="14"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
@@ -1283,7 +1291,7 @@
       </c>
       <c r="E46" s="7">
         <f>SUM(E3:E45)</f>
-        <v>697404.06</v>
+        <v>770038.06</v>
       </c>
       <c r="F46" s="8"/>
     </row>
@@ -1301,7 +1309,7 @@
       </c>
       <c r="E47" s="7">
         <f>E46/4</f>
-        <v>174351.01500000001</v>
+        <v>192509.51500000001</v>
       </c>
       <c r="F47" s="7"/>
     </row>
@@ -1319,7 +1327,7 @@
       </c>
       <c r="E48" s="7">
         <f>SUMIF(F3:F45, "Премия", E3:E45)</f>
-        <v>191331</v>
+        <v>228965</v>
       </c>
       <c r="F48" s="8"/>
     </row>
@@ -1337,7 +1345,7 @@
       </c>
       <c r="E49" s="10">
         <f>E48/E46</f>
-        <v>0.27434741346358088</v>
+        <v>0.29734244564482953</v>
       </c>
       <c r="F49" s="8"/>
     </row>

--- a/Другое/2026/Доходы.xlsx
+++ b/Другое/2026/Доходы.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="11">
   <si>
     <t>Дата</t>
   </si>
@@ -926,11 +926,15 @@
       <c r="C21" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="12"/>
+      <c r="D21" s="12">
+        <v>46223</v>
+      </c>
       <c r="E21" s="13">
-        <v>35000</v>
-      </c>
-      <c r="F21" s="14"/>
+        <v>36898.639999999999</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1">
       <c r="A22" s="3">
@@ -1291,7 +1295,7 @@
       </c>
       <c r="E46" s="7">
         <f>SUM(E3:E45)</f>
-        <v>770038.06</v>
+        <v>771936.70000000007</v>
       </c>
       <c r="F46" s="8"/>
     </row>
@@ -1309,7 +1313,7 @@
       </c>
       <c r="E47" s="7">
         <f>E46/4</f>
-        <v>192509.51500000001</v>
+        <v>192984.17500000002</v>
       </c>
       <c r="F47" s="7"/>
     </row>
@@ -1345,7 +1349,7 @@
       </c>
       <c r="E49" s="10">
         <f>E48/E46</f>
-        <v>0.29734244564482953</v>
+        <v>0.29661110813878905</v>
       </c>
       <c r="F49" s="8"/>
     </row>

--- a/Другое/2026/Доходы.xlsx
+++ b/Другое/2026/Доходы.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="13">
   <si>
     <t>Дата</t>
   </si>
@@ -49,6 +49,12 @@
   </si>
   <si>
     <t xml:space="preserve">% Премии от общего дохода: </t>
+  </si>
+  <si>
+    <t>ЗП + Премия</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -186,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -226,6 +232,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -530,7 +539,7 @@
     <col min="3" max="3" width="11.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="25.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -946,9 +955,16 @@
       <c r="C22" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="14"/>
+      <c r="D22" s="12">
+        <v>46239</v>
+      </c>
+      <c r="E22" s="13">
+        <f>18817.85+40252.26+37635</f>
+        <v>96705.11</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
       <c r="A23" s="3">
@@ -960,8 +976,12 @@
       <c r="C23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="13"/>
+      <c r="D23" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="13">
+        <v>0</v>
+      </c>
       <c r="F23" s="14"/>
     </row>
     <row r="24" spans="1:6" ht="15.75" thickBot="1">
@@ -975,8 +995,12 @@
       <c r="C24" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="13"/>
+      <c r="D24" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="13">
+        <v>0</v>
+      </c>
       <c r="F24" s="14"/>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1">
@@ -989,8 +1013,12 @@
       <c r="C25" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
+      <c r="D25" s="12">
+        <v>46254</v>
+      </c>
+      <c r="E25" s="13">
+        <v>0</v>
+      </c>
       <c r="F25" s="14"/>
     </row>
     <row r="26" spans="1:6" ht="15.75" thickBot="1">
@@ -1295,7 +1323,7 @@
       </c>
       <c r="E46" s="7">
         <f>SUM(E3:E45)</f>
-        <v>771936.70000000007</v>
+        <v>868641.81</v>
       </c>
       <c r="F46" s="8"/>
     </row>
@@ -1312,8 +1340,8 @@
         <v>8</v>
       </c>
       <c r="E47" s="7">
-        <f>E46/4</f>
-        <v>192984.17500000002</v>
+        <f>E46/8</f>
+        <v>108580.22625000001</v>
       </c>
       <c r="F47" s="7"/>
     </row>
@@ -1349,7 +1377,7 @@
       </c>
       <c r="E49" s="10">
         <f>E48/E46</f>
-        <v>0.29661110813878905</v>
+        <v>0.26358966073714546</v>
       </c>
       <c r="F49" s="8"/>
     </row>

--- a/Другое/2026/Доходы.xlsx
+++ b/Другое/2026/Доходы.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="13">
   <si>
     <t>Дата</t>
   </si>
@@ -64,7 +64,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +91,21 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Bahnschrift SemiBold"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
       <name val="Bahnschrift SemiBold"/>
       <family val="2"/>
       <charset val="204"/>
@@ -192,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -216,6 +231,9 @@
     <xf numFmtId="16" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -234,9 +252,10 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -531,7 +550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" style="1" customWidth="1"/>
@@ -540,7 +559,11 @@
     <col min="4" max="4" width="25.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.5703125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="1"/>
+    <col min="7" max="7" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="60.75" customHeight="1" thickBot="1">
@@ -564,16 +587,16 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="33" thickBot="1">
-      <c r="A2" s="15">
+      <c r="A2" s="16">
         <v>2025</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18">
+      <c r="B2" s="17"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="19">
         <v>2026</v>
       </c>
-      <c r="E2" s="19"/>
-      <c r="F2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1">
       <c r="A3" s="3">
@@ -850,7 +873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15.75" thickBot="1">
+    <row r="17" spans="1:10" ht="15.75" thickBot="1">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
@@ -864,7 +887,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="15.75" thickBot="1">
+    <row r="18" spans="1:10" ht="15.75" thickBot="1">
       <c r="A18" s="3">
         <v>46207</v>
       </c>
@@ -885,7 +908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="15.75" thickBot="1">
+    <row r="19" spans="1:10" ht="15.75" thickBot="1">
       <c r="A19" s="3">
         <v>46207</v>
       </c>
@@ -905,7 +928,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="15.75" thickBot="1">
+    <row r="20" spans="1:10" ht="15.75" thickBot="1">
       <c r="A20" s="3">
         <v>46212</v>
       </c>
@@ -925,7 +948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="15.75" thickBot="1">
+    <row r="21" spans="1:10" ht="15.75" thickBot="1">
       <c r="A21" s="3">
         <v>46221</v>
       </c>
@@ -945,7 +968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15.75" thickBot="1">
+    <row r="22" spans="1:10" ht="15.75" thickBot="1">
       <c r="A22" s="3">
         <v>46239</v>
       </c>
@@ -966,7 +989,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15.75" thickBot="1">
+    <row r="23" spans="1:10" ht="15.75" thickBot="1">
       <c r="A23" s="3">
         <v>46239</v>
       </c>
@@ -976,7 +999,7 @@
       <c r="C23" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="15" t="s">
         <v>12</v>
       </c>
       <c r="E23" s="13">
@@ -984,7 +1007,7 @@
       </c>
       <c r="F23" s="14"/>
     </row>
-    <row r="24" spans="1:6" ht="15.75" thickBot="1">
+    <row r="24" spans="1:10" ht="15.75" thickBot="1">
       <c r="A24" s="3">
         <v>46241</v>
       </c>
@@ -995,7 +1018,7 @@
       <c r="C24" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="15" t="s">
         <v>12</v>
       </c>
       <c r="E24" s="13">
@@ -1003,7 +1026,7 @@
       </c>
       <c r="F24" s="14"/>
     </row>
-    <row r="25" spans="1:6" ht="15.75" thickBot="1">
+    <row r="25" spans="1:10" ht="15.75" thickBot="1">
       <c r="A25" s="3">
         <v>46254</v>
       </c>
@@ -1017,11 +1040,13 @@
         <v>46254</v>
       </c>
       <c r="E25" s="13">
-        <v>0</v>
-      </c>
-      <c r="F25" s="14"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.75" thickBot="1">
+        <v>36738.04</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" thickBot="1">
       <c r="A26" s="3">
         <v>46261</v>
       </c>
@@ -1031,11 +1056,17 @@
       <c r="C26" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="14"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" thickBot="1">
+      <c r="D26" s="12">
+        <v>46269</v>
+      </c>
+      <c r="E26" s="24"/>
+      <c r="F26" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="23"/>
+      <c r="H26" s="22"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" thickBot="1">
       <c r="A27" s="3">
         <v>46270</v>
       </c>
@@ -1048,8 +1079,12 @@
       <c r="D27" s="12"/>
       <c r="E27" s="13"/>
       <c r="F27" s="14"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" thickBot="1">
+      <c r="G27" s="23"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" thickBot="1">
       <c r="A28" s="3">
         <v>46284</v>
       </c>
@@ -1064,7 +1099,7 @@
       <c r="E28" s="13"/>
       <c r="F28" s="14"/>
     </row>
-    <row r="29" spans="1:6" ht="15.75" thickBot="1">
+    <row r="29" spans="1:10" ht="15.75" thickBot="1">
       <c r="A29" s="3">
         <v>46284</v>
       </c>
@@ -1078,7 +1113,7 @@
       <c r="E29" s="13"/>
       <c r="F29" s="14"/>
     </row>
-    <row r="30" spans="1:6" ht="15.75" thickBot="1">
+    <row r="30" spans="1:10" ht="15.75" thickBot="1">
       <c r="A30" s="3">
         <v>46298</v>
       </c>
@@ -1093,7 +1128,7 @@
       <c r="E30" s="13"/>
       <c r="F30" s="14"/>
     </row>
-    <row r="31" spans="1:6" ht="15.75" thickBot="1">
+    <row r="31" spans="1:10" ht="15.75" thickBot="1">
       <c r="A31" s="3">
         <v>46298</v>
       </c>
@@ -1107,7 +1142,7 @@
       <c r="E31" s="13"/>
       <c r="F31" s="14"/>
     </row>
-    <row r="32" spans="1:6" ht="15.75" thickBot="1">
+    <row r="32" spans="1:10" ht="15.75" thickBot="1">
       <c r="A32" s="3">
         <v>46315</v>
       </c>
@@ -1323,7 +1358,7 @@
       </c>
       <c r="E46" s="7">
         <f>SUM(E3:E45)</f>
-        <v>868641.81</v>
+        <v>905379.85000000009</v>
       </c>
       <c r="F46" s="8"/>
     </row>
@@ -1341,7 +1376,7 @@
       </c>
       <c r="E47" s="7">
         <f>E46/8</f>
-        <v>108580.22625000001</v>
+        <v>113172.48125000001</v>
       </c>
       <c r="F47" s="7"/>
     </row>
@@ -1377,7 +1412,7 @@
       </c>
       <c r="E49" s="10">
         <f>E48/E46</f>
-        <v>0.26358966073714546</v>
+        <v>0.2528938544413154</v>
       </c>
       <c r="F49" s="8"/>
     </row>

--- a/Другое/2026/Доходы.xlsx
+++ b/Другое/2026/Доходы.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="13">
   <si>
     <t>Дата</t>
   </si>
@@ -64,7 +64,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;₽&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,13 +102,6 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFF00"/>
-      <name val="Bahnschrift SemiBold"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="6">
@@ -207,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -234,6 +227,9 @@
     <xf numFmtId="16" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -252,10 +248,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -587,16 +579,16 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="33" thickBot="1">
-      <c r="A2" s="16">
+      <c r="A2" s="19">
         <v>2025</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19">
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="22">
         <v>2026</v>
       </c>
-      <c r="E2" s="20"/>
-      <c r="F2" s="21"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1">
       <c r="A3" s="3">
@@ -1059,12 +1051,14 @@
       <c r="D26" s="12">
         <v>46269</v>
       </c>
-      <c r="E26" s="24"/>
+      <c r="E26" s="13">
+        <v>66577.47</v>
+      </c>
       <c r="F26" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="G26" s="23"/>
-      <c r="H26" s="22"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="16"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" thickBot="1">
       <c r="A27" s="3">
@@ -1076,13 +1070,19 @@
       <c r="C27" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
+      <c r="D27" s="12">
+        <v>46269</v>
+      </c>
+      <c r="E27" s="13">
+        <v>18817</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="17"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" thickBot="1">
       <c r="A28" s="3">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="E46" s="7">
         <f>SUM(E3:E45)</f>
-        <v>905379.85000000009</v>
+        <v>990774.32000000007</v>
       </c>
       <c r="F46" s="8"/>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="E47" s="7">
         <f>E46/8</f>
-        <v>113172.48125000001</v>
+        <v>123846.79000000001</v>
       </c>
       <c r="F47" s="7"/>
     </row>
@@ -1394,7 +1394,7 @@
       </c>
       <c r="E48" s="7">
         <f>SUMIF(F3:F45, "Премия", E3:E45)</f>
-        <v>228965</v>
+        <v>247782</v>
       </c>
       <c r="F48" s="8"/>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E49" s="10">
         <f>E48/E46</f>
-        <v>0.2528938544413154</v>
+        <v>0.25008924333040844</v>
       </c>
       <c r="F49" s="8"/>
     </row>
